--- a/data/malingas.xlsx
+++ b/data/malingas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,25 +457,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -500,18 +515,27 @@
         <v>55</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>14</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>15</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>27</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>13</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -534,18 +558,27 @@
         <v>22</v>
       </c>
       <c r="F3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>17</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>27</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>20</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -568,18 +601,27 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H4" t="n">
         <v>14</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J4" t="n">
         <v>15</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>35</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -608,12 +650,21 @@
         <v>15</v>
       </c>
       <c r="H5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" t="n">
         <v>19</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>24</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -636,18 +687,27 @@
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>15</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>15</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>23</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -670,18 +730,27 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
         <v>15</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>41</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -704,18 +773,27 @@
         <v>28</v>
       </c>
       <c r="F8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" t="n">
         <v>10</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
         <v>17</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>15</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>18</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>40</v>
       </c>
     </row>
@@ -738,18 +816,27 @@
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>25</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>15</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>15</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -772,18 +859,27 @@
         <v>46</v>
       </c>
       <c r="F10" t="n">
+        <v>23</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="n">
         <v>14</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>15</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>19</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>16</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -806,18 +902,27 @@
         <v>24</v>
       </c>
       <c r="F11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" t="n">
         <v>13</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13</v>
+      </c>
+      <c r="J11" t="n">
         <v>15</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>40</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -854,6 +959,15 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -874,18 +988,27 @@
         <v>16</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>11</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>16</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>24</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>17</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -908,18 +1031,27 @@
         <v>65</v>
       </c>
       <c r="F14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" t="n">
         <v>10</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>15</v>
       </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>15</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>24</v>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -942,18 +1074,27 @@
         <v>35</v>
       </c>
       <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
         <v>13</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>18</v>
       </c>
-      <c r="H15" t="n">
+      <c r="K15" t="n">
         <v>16</v>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
         <v>27</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -976,18 +1117,27 @@
         <v>23</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>17</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>25</v>
       </c>
-      <c r="H16" t="n">
+      <c r="K16" t="n">
         <v>23</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>13</v>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1002,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,25 +1183,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1079,27 +1244,34 @@
           <t>55</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1129,25 +1301,40 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1179,27 +1366,38 @@
           <t>48</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -1239,15 +1437,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1279,23 +1488,34 @@
           <t>24</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1323,19 +1543,30 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1369,25 +1600,36 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1419,23 +1661,34 @@
           <t>22</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1461,25 +1714,40 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1513,21 +1781,36 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1552,6 +1835,9 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1579,27 +1865,34 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1625,25 +1918,40 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1673,25 +1981,40 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1723,23 +2046,38 @@
           <t>23</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>27</t>
         </is>

--- a/data/malingas.xlsx
+++ b/data/malingas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,25 +472,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -524,18 +534,24 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
         <v>14</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>15</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>27</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>13</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -567,18 +583,24 @@
         <v>13</v>
       </c>
       <c r="I3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>17</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>27</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>20</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -610,18 +632,24 @@
         <v>14</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>14</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>15</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>35</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>13</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -653,18 +681,24 @@
         <v>50</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>15</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>19</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>24</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -699,15 +733,21 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>15</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>23</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -739,18 +779,24 @@
         <v>9</v>
       </c>
       <c r="I7" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
         <v>15</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>41</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -764,7 +810,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
         <v>22</v>
@@ -782,18 +828,24 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>17</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>15</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>18</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>40</v>
       </c>
     </row>
@@ -825,18 +877,24 @@
         <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>15</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>15</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -868,18 +926,24 @@
         <v>13</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
         <v>14</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>15</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>19</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>16</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -911,18 +975,24 @@
         <v>25</v>
       </c>
       <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>13</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>15</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>40</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -968,6 +1038,12 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -997,18 +1073,24 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20</v>
+      </c>
+      <c r="K13" t="n">
         <v>11</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>16</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>24</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>17</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1040,18 +1122,24 @@
         <v>9</v>
       </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="n">
         <v>10</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>15</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>15</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>24</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1083,18 +1171,24 @@
         <v>10</v>
       </c>
       <c r="I15" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="n">
         <v>13</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>18</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>16</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>27</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1126,18 +1220,24 @@
         <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>25</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>23</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>13</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1152,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,25 +1298,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1253,25 +1363,35 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1316,25 +1436,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1377,27 +1507,29 @@
           <t>14</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -1440,23 +1572,33 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1502,20 +1644,26 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1556,18 +1704,28 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
@@ -1585,7 +1743,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1611,25 +1769,35 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1672,23 +1840,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1727,27 +1905,33 @@
           <t>13</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1796,21 +1980,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1838,6 +2028,8 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1874,25 +2066,35 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1931,27 +2133,33 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1996,25 +2204,35 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -2061,23 +2279,29 @@
           <t>17</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>27</t>
         </is>

--- a/data/malingas.xlsx
+++ b/data/malingas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,25 +482,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -540,18 +545,21 @@
         <v>6</v>
       </c>
       <c r="K2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" t="n">
         <v>14</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>15</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>27</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>13</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -589,18 +597,21 @@
         <v>10</v>
       </c>
       <c r="K3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>17</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>27</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>20</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -638,18 +649,21 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" t="n">
         <v>14</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>15</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>35</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>13</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -687,18 +701,21 @@
         <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>15</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>19</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>24</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -736,18 +753,21 @@
         <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>15</v>
       </c>
       <c r="N6" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" t="n">
         <v>23</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -785,18 +805,21 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
+        <v>19</v>
+      </c>
+      <c r="L7" t="n">
         <v>15</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>41</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -837,15 +860,18 @@
         <v>10</v>
       </c>
       <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
         <v>17</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>15</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>18</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>40</v>
       </c>
     </row>
@@ -883,18 +909,21 @@
         <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>15</v>
       </c>
       <c r="N9" t="n">
         <v>15</v>
       </c>
       <c r="O9" t="n">
+        <v>15</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -932,18 +961,21 @@
         <v>7</v>
       </c>
       <c r="K10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L10" t="n">
         <v>14</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>15</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>19</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>16</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -981,18 +1013,21 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>27</v>
+      </c>
+      <c r="L11" t="n">
         <v>13</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>15</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>40</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1044,6 +1079,9 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1079,18 +1117,21 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
         <v>11</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>16</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>24</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>17</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,18 +1169,21 @@
         <v>8</v>
       </c>
       <c r="K14" t="n">
+        <v>14</v>
+      </c>
+      <c r="L14" t="n">
         <v>10</v>
-      </c>
-      <c r="L14" t="n">
-        <v>15</v>
       </c>
       <c r="M14" t="n">
         <v>15</v>
       </c>
       <c r="N14" t="n">
+        <v>15</v>
+      </c>
+      <c r="O14" t="n">
         <v>24</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1171,24 +1215,27 @@
         <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
         <v>8</v>
       </c>
       <c r="K15" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" t="n">
         <v>13</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>18</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>16</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>27</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1226,18 +1273,21 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>25</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>23</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>13</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1252,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,25 +1358,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1373,25 +1428,30 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1446,25 +1506,30 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1511,25 +1576,30 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -1582,23 +1652,28 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1647,23 +1722,28 @@
           <t>9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1714,17 +1794,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1784,20 +1869,25 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1850,23 +1940,28 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1913,25 +2008,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -1986,21 +2086,26 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2030,6 +2135,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2076,25 +2182,30 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2141,25 +2252,30 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2204,7 +2320,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2214,25 +2330,30 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -2285,23 +2406,28 @@
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>27</t>
         </is>

--- a/data/malingas.xlsx
+++ b/data/malingas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,25 +487,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -548,18 +553,21 @@
         <v>12</v>
       </c>
       <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
         <v>14</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>15</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>27</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>13</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -600,18 +608,21 @@
         <v>13</v>
       </c>
       <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
         <v>12</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>17</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>27</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>20</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -652,18 +663,21 @@
         <v>18</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>14</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>15</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>35</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>13</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -704,18 +718,21 @@
         <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>15</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>19</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>24</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -756,18 +773,21 @@
         <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>15</v>
       </c>
       <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
         <v>23</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -808,18 +828,21 @@
         <v>19</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>15</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>41</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -860,18 +883,21 @@
         <v>10</v>
       </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>17</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>15</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>18</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>40</v>
       </c>
     </row>
@@ -912,18 +938,21 @@
         <v>19</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15</v>
       </c>
       <c r="O9" t="n">
         <v>15</v>
       </c>
       <c r="P9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -964,18 +993,21 @@
         <v>11</v>
       </c>
       <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
         <v>14</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>15</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>19</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>16</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1016,18 +1048,21 @@
         <v>27</v>
       </c>
       <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
         <v>13</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>15</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>40</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1082,6 +1117,9 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1120,18 +1158,21 @@
         <v>10</v>
       </c>
       <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
         <v>11</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>16</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>24</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>17</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1172,18 +1213,21 @@
         <v>14</v>
       </c>
       <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
         <v>10</v>
-      </c>
-      <c r="M14" t="n">
-        <v>15</v>
       </c>
       <c r="N14" t="n">
         <v>15</v>
       </c>
       <c r="O14" t="n">
+        <v>15</v>
+      </c>
+      <c r="P14" t="n">
         <v>24</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1224,18 +1268,21 @@
         <v>12</v>
       </c>
       <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
         <v>13</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>18</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>16</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>27</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1276,18 +1323,21 @@
         <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>25</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>23</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>13</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1302,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,25 +1413,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1433,25 +1488,30 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1511,25 +1571,30 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1579,27 +1644,28 @@
           <t>18</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -1657,23 +1723,28 @@
           <t>17</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1727,23 +1798,28 @@
           <t>17</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1797,19 +1873,20 @@
           <t>19</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1869,25 +1946,30 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -1945,23 +2027,28 @@
           <t>19</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2013,25 +2100,30 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -2091,21 +2183,26 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2136,6 +2233,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2187,25 +2285,30 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2257,25 +2360,30 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2335,25 +2443,30 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -2411,23 +2524,28 @@
           <t>17</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>27</t>
         </is>

--- a/data/malingas.xlsx
+++ b/data/malingas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,25 +492,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -556,18 +571,27 @@
         <v>2</v>
       </c>
       <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
         <v>14</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>15</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>27</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>13</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -611,18 +635,27 @@
         <v>2</v>
       </c>
       <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
         <v>12</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>17</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>27</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>20</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -666,18 +699,27 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>14</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>15</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>35</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>13</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -721,18 +763,27 @@
         <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>15</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>19</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>24</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -776,18 +827,27 @@
         <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>15</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>15</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>23</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>8</v>
       </c>
     </row>
@@ -831,18 +891,27 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>15</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>41</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -886,18 +955,27 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>17</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>15</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>18</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>40</v>
       </c>
     </row>
@@ -944,15 +1022,24 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>25</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>15</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>15</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -996,18 +1083,27 @@
         <v>2</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>14</v>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>15</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>19</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>16</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1051,18 +1147,27 @@
         <v>4</v>
       </c>
       <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>13</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>15</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>40</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1120,6 +1225,15 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1161,18 +1275,27 @@
         <v>3</v>
       </c>
       <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
         <v>11</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>16</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>24</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>17</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1216,18 +1339,27 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>10</v>
       </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
         <v>15</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>15</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>24</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1271,18 +1403,27 @@
         <v>2</v>
       </c>
       <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
         <v>13</v>
       </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
         <v>18</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
         <v>16</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
         <v>27</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1326,18 +1467,27 @@
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>25</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>23</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>13</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1352,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,25 +1568,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1493,25 +1658,40 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1576,25 +1756,40 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -1647,25 +1842,36 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -1728,23 +1934,38 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1803,23 +2024,34 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1876,17 +2108,28 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1949,27 +2192,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -2035,20 +2285,27 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2103,27 +2360,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -2188,21 +2452,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2234,6 +2509,9 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2290,25 +2568,40 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2365,25 +2658,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2448,25 +2748,40 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -2529,23 +2844,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>27</t>
         </is>

--- a/data/malingas.xlsx
+++ b/data/malingas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,25 +507,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -534,291 +539,303 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
+          <t>47356835</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="M2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>14</v>
-      </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ALAMA NIMA CLARITZA MABEL</t>
+          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
       </c>
       <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="n">
         <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
+        <v>15</v>
+      </c>
+      <c r="S3" t="n">
         <v>27</v>
       </c>
-      <c r="S3" t="n">
-        <v>20</v>
-      </c>
       <c r="T3" t="n">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ALBIRENA GARCIA ANGEELO ALONSO</t>
+          <t>ALAMA NIMA CLARITZA MABEL</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
         <v>21</v>
       </c>
-      <c r="C4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>18</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>14</v>
-      </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="T4" t="n">
-        <v>48</v>
+        <v>20</v>
+      </c>
+      <c r="U4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ATOCHE PALACIOS LUIS ANGEL</t>
+          <t>ALBIRENA GARCIA ANGEELO ALONSO</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>18</v>
       </c>
-      <c r="C5" t="n">
-        <v>33</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" t="n">
-        <v>27</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14</v>
+      </c>
+      <c r="R5" t="n">
         <v>15</v>
       </c>
-      <c r="H5" t="n">
-        <v>50</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>19</v>
-      </c>
       <c r="S5" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="T5" t="n">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="U5" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>BERNAOLA CARMEN ZUMIKO YASHURY</t>
+          <t>ATOCHE PALACIOS LUIS ANGEL</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>27</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>15</v>
       </c>
-      <c r="C6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D6" t="n">
-        <v>25</v>
-      </c>
-      <c r="E6" t="n">
-        <v>24</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>17</v>
@@ -827,202 +844,211 @@
         <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>15</v>
       </c>
       <c r="S6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="T6" t="n">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CARREÑO PALACIOS KATHERINE DE LOS MILAGROS</t>
+          <t>BERNAOLA CARMEN ZUMIKO YASHURY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>15</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>23</v>
+      </c>
+      <c r="U7" t="n">
         <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>20</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>24</v>
-      </c>
-      <c r="H7" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" t="n">
-        <v>19</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>41</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CORDOVA CARMEN ANGIE NATALLY</t>
+          <t>CARREÑO PALACIOS KATHERINE DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>20</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>14</v>
-      </c>
-      <c r="K8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>17</v>
-      </c>
-      <c r="R8" t="n">
-        <v>15</v>
-      </c>
-      <c r="S8" t="n">
-        <v>18</v>
-      </c>
-      <c r="T8" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>JUAREZ CARMEN PIERRE ALEXANDER</t>
+          <t>CORDOVA CARMEN ANGIE NATALLY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" t="n">
         <v>10</v>
       </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19</v>
-      </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1031,437 +1057,458 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="U9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MANUEL LEUNARDO PRADO BAILON</t>
+          <t>JUAREZ CARMEN PIERRE ALEXANDER</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>39</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
         <v>9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>14</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>46</v>
-      </c>
-      <c r="F10" t="n">
-        <v>23</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>13</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>25</v>
+      </c>
+      <c r="S10" t="n">
         <v>15</v>
       </c>
-      <c r="R10" t="n">
-        <v>19</v>
-      </c>
-      <c r="S10" t="n">
-        <v>16</v>
-      </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MARYURI OJEDA VALLE</t>
+          <t>MANUEL LEUNARDO PRADO BAILON</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>46</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+      <c r="R11" t="n">
+        <v>15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>19</v>
+      </c>
+      <c r="T11" t="n">
         <v>16</v>
       </c>
-      <c r="C11" t="n">
-        <v>31</v>
-      </c>
-      <c r="D11" t="n">
-        <v>33</v>
-      </c>
-      <c r="E11" t="n">
-        <v>24</v>
-      </c>
-      <c r="F11" t="n">
-        <v>16</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13</v>
-      </c>
-      <c r="H11" t="n">
-        <v>25</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>27</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>15</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>40</v>
-      </c>
-      <c r="T11" t="n">
-        <v>12</v>
+      <c r="U11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>PIÑIN MACHUCA GIANCARLO</t>
+          <t>MARYURI OJEDA VALLE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="U12" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
+          <t>PIÑIN MACHUCA GIANCARLO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>RUIDIAS FRIAS MELISSA VICTORIA</t>
+          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S14" t="n">
         <v>24</v>
       </c>
       <c r="T14" t="n">
+        <v>17</v>
+      </c>
+      <c r="U14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>URRIOLA ARISMENDIZ INGRID MARYURI</t>
+          <t>RUIDIAS FRIAS MELISSA VICTORIA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="T15" t="n">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>VEGA ROBLEDO FERNANDO ERNESTO</t>
+          <t>URRIOLA ARISMENDIZ INGRID MARYURI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -1470,24 +1517,94 @@
         <v>2</v>
       </c>
       <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>13</v>
+      </c>
+      <c r="R16" t="n">
+        <v>18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>27</v>
+      </c>
+      <c r="U16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>VEGA ROBLEDO FERNANDO ERNESTO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" t="n">
+        <v>22</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>17</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>25</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S17" t="n">
         <v>23</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T17" t="n">
         <v>13</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U17" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1502,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,25 +1700,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1610,645 +1732,612 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>47356835</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ALAMA NIMA CLARITZA MABEL</t>
+          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ALBIRENA GARCIA ANGEELO ALONSO</t>
+          <t>ALAMA NIMA CLARITZA MABEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ATOCHE PALACIOS LUIS ANGEL</t>
+          <t>ALBIRENA GARCIA ANGEELO ALONSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>BERNAOLA CARMEN ZUMIKO YASHURY</t>
+          <t>ATOCHE PALACIOS LUIS ANGEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CARREÑO PALACIOS KATHERINE DE LOS MILAGROS</t>
+          <t>BERNAOLA CARMEN ZUMIKO YASHURY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>24</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CORDOVA CARMEN ANGIE NATALLY</t>
+          <t>CARREÑO PALACIOS KATHERINE DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>JUAREZ CARMEN PIERRE ALEXANDER</t>
+          <t>CORDOVA CARMEN ANGIE NATALLY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2256,95 +2345,108 @@
           <t>11</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MANUEL LEUNARDO PRADO BAILON</t>
+          <t>JUAREZ CARMEN PIERRE ALEXANDER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>7</t>
@@ -2352,330 +2454,342 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MARYURI OJEDA VALLE</t>
+          <t>MANUEL LEUNARDO PRADO BAILON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>PIÑIN MACHUCA GIANCARLO</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>MARYURI OJEDA VALLE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>PIÑIN MACHUCA GIANCARLO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>RUIDIAS FRIAS MELISSA VICTORIA</t>
+          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2683,32 +2797,33 @@
           <t>24</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>URRIOLA ARISMENDIZ INGRID MARYURI</t>
+          <t>RUIDIAS FRIAS MELISSA VICTORIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2718,160 +2833,261 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>URRIOLA ARISMENDIZ INGRID MARYURI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>VEGA ROBLEDO FERNANDO ERNESTO</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>27</t>
         </is>

--- a/data/malingas.xlsx
+++ b/data/malingas.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,25 +512,30 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>16dec2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -602,6 +607,9 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -655,18 +663,21 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>14</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>15</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>27</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>13</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -722,18 +733,21 @@
         <v>3</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>12</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>17</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>27</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>20</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -789,18 +803,21 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>14</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>15</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>35</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>13</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>48</v>
       </c>
     </row>
@@ -859,15 +876,18 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>15</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>19</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>24</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>16</v>
       </c>
     </row>
@@ -923,18 +943,21 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
       </c>
       <c r="T7" t="n">
+        <v>15</v>
+      </c>
+      <c r="U7" t="n">
         <v>23</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>8</v>
       </c>
     </row>
@@ -990,18 +1013,21 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>15</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>41</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1057,18 +1083,21 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>10</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>17</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>15</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>18</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1127,15 +1156,18 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>15</v>
       </c>
       <c r="T10" t="n">
         <v>15</v>
       </c>
       <c r="U10" t="n">
+        <v>15</v>
+      </c>
+      <c r="V10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1191,18 +1223,21 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
         <v>14</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>15</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>19</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>16</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1258,18 +1293,21 @@
         <v>5</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>13</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>15</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
         <v>40</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1339,6 +1377,9 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1392,18 +1433,21 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>11</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>16</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>24</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>17</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1459,18 +1503,21 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>10</v>
-      </c>
-      <c r="R15" t="n">
-        <v>15</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
       </c>
       <c r="T15" t="n">
+        <v>15</v>
+      </c>
+      <c r="U15" t="n">
         <v>24</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1526,18 +1573,21 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>13</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>18</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>16</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>27</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1596,15 +1646,18 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>25</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>23</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>13</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1619,7 +1672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1705,25 +1758,30 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>16dec2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1759,6 +1817,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1831,25 +1890,30 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1932,27 +1996,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -2019,27 +2084,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -2123,22 +2189,23 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -2213,23 +2280,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2296,19 +2368,20 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2379,27 +2452,28 @@
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -2475,22 +2549,23 @@
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2559,25 +2634,30 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -2656,23 +2736,24 @@
           <t>5</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2708,6 +2789,7 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2782,27 +2864,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2869,27 +2952,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2972,27 +3056,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -3072,22 +3157,23 @@
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>27</t>
         </is>
